--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:34</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
@@ -36,48 +36,48 @@
     <t xml:space="preserve">Coquimbo</t>
   </si>
   <si>
+    <t xml:space="preserve">Río Hurtado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punitaqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combarbalá</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canela</t>
   </si>
   <si>
+    <t xml:space="preserve">Vicuña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andacollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Serena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Vilos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salamanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">La Higuera</t>
   </si>
   <si>
-    <t xml:space="preserve">La Serena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Hurtado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Vilos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salamanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Punitaqui</t>
-  </si>
-  <si>
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Andacollo</t>
+    <t xml:space="preserve">Monte Patria</t>
   </si>
   <si>
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
-    <t xml:space="preserve">Monte Patria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vicuña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combarbalá</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,13 +517,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4202</v>
+        <v>4305</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.32</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
@@ -534,13 +534,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4104</v>
+        <v>4304</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7.97</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="4">
@@ -551,13 +551,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4101</v>
+        <v>4302</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.96</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="5">
@@ -568,13 +568,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4105</v>
+        <v>4202</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="6">
@@ -585,13 +585,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4305</v>
+        <v>4106</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.29</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="7">
@@ -599,16 +599,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4102</v>
+        <v>4103</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.09</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="8">
@@ -616,16 +616,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4203</v>
+        <v>4101</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.07</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="9">
@@ -633,16 +633,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4204</v>
+        <v>4203</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="10">
@@ -650,16 +650,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4304</v>
+        <v>4204</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -667,16 +667,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4201</v>
+        <v>4105</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.57</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="12">
@@ -684,16 +684,16 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.28</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="13">
@@ -704,13 +704,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4301</v>
+        <v>4104</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.26</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="14">
@@ -721,13 +721,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4303</v>
+        <v>4201</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.21</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="15">
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4106</v>
+        <v>4303</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.56</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="16">
@@ -755,13 +755,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4302</v>
+        <v>4301</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.18</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:29</t>
+    <t xml:space="preserve">2026-09-27 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.95</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.06</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.74</v>
+        <v>37.39</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.53</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.79</v>
+        <v>27.91</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.42</v>
+        <v>24.17</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.16</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="9">
@@ -642,7 +642,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.91</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.48</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="12">
@@ -693,7 +693,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.01</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.96</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +727,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.93</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="15">
@@ -744,7 +744,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.85</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="16">
@@ -761,7 +761,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.18</v>
+        <v>-1.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:26</t>
+    <t xml:space="preserve">2026-10-04 08:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:16</t>
+    <t xml:space="preserve">2026-10-05 08:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
